--- a/ejemplos/japon-2026-hitos.xlsx
+++ b/ejemplos/japon-2026-hitos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L347"/>
+  <dimension ref="A1:L351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8936,6 +8936,106 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Ōya History Museum</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Cantera industrial de piedra Ōya (1919–1986)</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Utsunomiya</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>1979</v>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>S · Antigua cantera subterránea: una arquitectura del vacío, la escala y la temperatura. No es obra de autor, pero espacialmente es brutal</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Stone Plaza</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Kengo Kuma</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Nasu</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>A+/S− · Tres almacenes de piedra transformados mediante muros porosos, lamas pétreas, agua y luz. Encaja extraordinariamente bien antes de Ishigami (Water Garden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Nasu History Museum</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Kengo Kuma</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Nasu</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>A · Pequeño, transparente y casi desmaterializado; a unos diez minutos andando de Stone Plaza</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Suite Villas (Art Biotop Nasu)</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Shigeru Ban</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Nasu</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>2018</v>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>A+ si permiten visita [R] · En el propio complejo de Water Garden: catorce villas de madera con estructura de grandes cerchas y piedra excavada del solar. Preguntar si permiten visita</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ejemplos/japon-2026-hitos.xlsx
+++ b/ejemplos/japon-2026-hitos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L351"/>
+  <dimension ref="A1:L361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9036,6 +9036,256 @@
         </is>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Kurkku Fields</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Hiroshi Nakamura &amp; NAP</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Kisarazu</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>2023</v>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>A · Chiba, ~1 h de Tokio por el Aqua-Line. Granja-parque con la Biblioteca subterránea (Library in the Earth, 2023) y las cabañas Cocoon de Nakamura &amp; NAP; también obras de arte en el paisaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Tanikawa House</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Kazuo Shinohara</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Naganohara</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>1974</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>S [R] · Kita-Karuizawa (Gunma). Casa del poeta Tanikawa: el suelo en pendiente de tierra bajo la gran cubierta; obra clave de la tercera etapa de Shinohara. Privada: visitas solo en jornadas concertadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Shiraiwa Sake Brewery</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Kengo Kuma</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Tateyama</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>2021</v>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>A [R] · Bodega IWA (Richard Geoffroy) en Shiraiwa, falda del Tateyama, Toyama: una sola cubierta negra baja contra los arrozales. Visita con reserva</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Ebara Hatakeyama Museum of Art</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>New Material Research Laboratory (Hiroshi Sugimoto y Tomoyuki Sakakida) · Taisei</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Tokio</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>A · Shirokanedai, Tokio. Reabierto en octubre de 2024 tras 4,5 años de obra: edificio principal reformado y ala nueva; jardín con casas de té</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Pilotis in a Forest</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Go Hasegawa</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Naganohara</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>2010</v>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>S [R] · Kita-Karuizawa (Gunma). Privada; hay que solicitar acceso</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>House in a Forest</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Go Hasegawa</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Karuizawa</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>2006</v>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>S− [R] · Privada; hay que solicitar acceso</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Roof on a Ridge</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Go Hasegawa</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Nagano</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>2020</v>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>A+ [R] · Nagano, ubicación no pública. Privada; preguntar si coincide geográficamente con la ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>space Un Tokyo</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Go Hasegawa</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Tokio</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>A/A+ · Aoyama. Pública</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Sanseido Jimbocho</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Go Hasegawa</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Tokio</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>A · Jimbōchō. Pública y facilísima</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Nippon Design Center</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Go Hasegawa</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Tokio</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>2012</v>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>A+ [R] · Ginza. Oficina; acceso académico negociable</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
